--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/120.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/120.xlsx
@@ -426,13 +426,13 @@
         <v>-22.42891771002927</v>
       </c>
       <c r="E2">
-        <v>-23.59594536571533</v>
+        <v>-30.26854036550944</v>
       </c>
       <c r="F2">
-        <v>-2.701073476536509</v>
+        <v>-4.557420803555519</v>
       </c>
       <c r="G2">
-        <v>-18.90539834451603</v>
+        <v>-18.44397012399348</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.82224039324488</v>
       </c>
       <c r="E3">
-        <v>-23.9132631705662</v>
+        <v>-30.47643766479638</v>
       </c>
       <c r="F3">
-        <v>-3.743233393957136</v>
+        <v>-4.444889576987415</v>
       </c>
       <c r="G3">
-        <v>-19.45965681046479</v>
+        <v>-18.19652375164776</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.91995739977408</v>
       </c>
       <c r="E4">
-        <v>-24.60761780590766</v>
+        <v>-30.70110147820165</v>
       </c>
       <c r="F4">
-        <v>-2.781150096630332</v>
+        <v>-4.542375994785875</v>
       </c>
       <c r="G4">
-        <v>-17.9508239674335</v>
+        <v>-17.93340899563848</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.82662988792571</v>
       </c>
       <c r="E5">
-        <v>-25.54916327288027</v>
+        <v>-30.59775089098896</v>
       </c>
       <c r="F5">
-        <v>-2.288915961804004</v>
+        <v>-4.552002452373809</v>
       </c>
       <c r="G5">
-        <v>-16.72587174288921</v>
+        <v>-17.9382219032922</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.56211423524752</v>
       </c>
       <c r="E6">
-        <v>-24.73029951523177</v>
+        <v>-31.41784607579526</v>
       </c>
       <c r="F6">
-        <v>-2.56049869991403</v>
+        <v>-4.335332189395361</v>
       </c>
       <c r="G6">
-        <v>-16.27836923401567</v>
+        <v>-18.03359109783327</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.20214089314636</v>
       </c>
       <c r="E7">
-        <v>-26.6978003161428</v>
+        <v>-32.22249131447321</v>
       </c>
       <c r="F7">
-        <v>-2.745406043199533</v>
+        <v>-4.541693420045968</v>
       </c>
       <c r="G7">
-        <v>-17.08693771984018</v>
+        <v>-17.44846318783919</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.79631782191711</v>
       </c>
       <c r="E8">
-        <v>-25.53662472789061</v>
+        <v>-32.06810398989536</v>
       </c>
       <c r="F8">
-        <v>-2.724667036903044</v>
+        <v>-4.310516787109696</v>
       </c>
       <c r="G8">
-        <v>-16.77638965072726</v>
+        <v>-17.25313249902127</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.40697693011604</v>
       </c>
       <c r="E9">
-        <v>-25.14619794408878</v>
+        <v>-32.85696910214462</v>
       </c>
       <c r="F9">
-        <v>-3.03545309071796</v>
+        <v>-4.212916882977053</v>
       </c>
       <c r="G9">
-        <v>-16.93414911413446</v>
+        <v>-17.06670314388676</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.09950390432364</v>
       </c>
       <c r="E10">
-        <v>-26.42787895893087</v>
+        <v>-32.81529993292261</v>
       </c>
       <c r="F10">
-        <v>-2.637135110184026</v>
+        <v>-4.432296735730057</v>
       </c>
       <c r="G10">
-        <v>-16.1272410618699</v>
+        <v>-16.65527329302862</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.93108591641333</v>
       </c>
       <c r="E11">
-        <v>-26.5463326991263</v>
+        <v>-33.92935318548329</v>
       </c>
       <c r="F11">
-        <v>-2.374487971247998</v>
+        <v>-4.341872150040463</v>
       </c>
       <c r="G11">
-        <v>-15.14077121811774</v>
+        <v>-16.27792279669059</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.96733365747828</v>
       </c>
       <c r="E12">
-        <v>-27.7558018286636</v>
+        <v>-33.688911322255</v>
       </c>
       <c r="F12">
-        <v>-1.987672700469338</v>
+        <v>-4.287032571240331</v>
       </c>
       <c r="G12">
-        <v>-14.45693627662285</v>
+        <v>-15.72885188024437</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.23172031909978</v>
       </c>
       <c r="E13">
-        <v>-28.80433609596945</v>
+        <v>-34.13128024349079</v>
       </c>
       <c r="F13">
-        <v>-2.519545872254428</v>
+        <v>-4.314439106761952</v>
       </c>
       <c r="G13">
-        <v>-14.75691735700324</v>
+        <v>-15.7060457208687</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.737289980418826</v>
       </c>
       <c r="E14">
-        <v>-30.01506780174949</v>
+        <v>-34.58373523842894</v>
       </c>
       <c r="F14">
-        <v>-2.174863024316957</v>
+        <v>-3.780888490986193</v>
       </c>
       <c r="G14">
-        <v>-12.24068302546055</v>
+        <v>-15.41253537095738</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.462363778729136</v>
       </c>
       <c r="E15">
-        <v>-29.49572741503064</v>
+        <v>-35.90787245603909</v>
       </c>
       <c r="F15">
-        <v>-2.201509118562808</v>
+        <v>-3.869968636381043</v>
       </c>
       <c r="G15">
-        <v>-12.88556043616685</v>
+        <v>-15.29301287283162</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.366241352072043</v>
       </c>
       <c r="E16">
-        <v>-31.22638511032633</v>
+        <v>-35.76164619171453</v>
       </c>
       <c r="F16">
-        <v>-1.514013876283387</v>
+        <v>-3.802113748948125</v>
       </c>
       <c r="G16">
-        <v>-12.79915392780707</v>
+        <v>-14.56338416583631</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.40478146800441</v>
       </c>
       <c r="E17">
-        <v>-32.31107308221481</v>
+        <v>-36.36192851394296</v>
       </c>
       <c r="F17">
-        <v>-2.256806784536689</v>
+        <v>-3.844925433059609</v>
       </c>
       <c r="G17">
-        <v>-12.85983154822143</v>
+        <v>-14.62588016985838</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.515020231726252</v>
       </c>
       <c r="E18">
-        <v>-32.92809699929363</v>
+        <v>-37.15709404777198</v>
       </c>
       <c r="F18">
-        <v>-1.288824682934549</v>
+        <v>-3.492864316665402</v>
       </c>
       <c r="G18">
-        <v>-12.0302322093432</v>
+        <v>-14.06936993669978</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.647335120844717</v>
       </c>
       <c r="E19">
-        <v>-32.93736696697064</v>
+        <v>-37.24285786162969</v>
       </c>
       <c r="F19">
-        <v>-2.075727327019523</v>
+        <v>-3.61325840662088</v>
       </c>
       <c r="G19">
-        <v>-12.14744811462271</v>
+        <v>-13.91915160904401</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.744101511962418</v>
       </c>
       <c r="E20">
-        <v>-31.86795865954621</v>
+        <v>-37.6432585824281</v>
       </c>
       <c r="F20">
-        <v>-1.485886661121329</v>
+        <v>-3.556534291979378</v>
       </c>
       <c r="G20">
-        <v>-11.93080069621836</v>
+        <v>-13.59726246542729</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.768054968267997</v>
       </c>
       <c r="E21">
-        <v>-35.16503530829724</v>
+        <v>-38.12808578303762</v>
       </c>
       <c r="F21">
-        <v>-1.55322713239711</v>
+        <v>-3.50683307617881</v>
       </c>
       <c r="G21">
-        <v>-11.97392105925748</v>
+        <v>-13.76522602406886</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.693823934273478</v>
       </c>
       <c r="E22">
-        <v>-34.47748570971152</v>
+        <v>-38.74990458259095</v>
       </c>
       <c r="F22">
-        <v>-1.695080908289511</v>
+        <v>-3.20728382618287</v>
       </c>
       <c r="G22">
-        <v>-11.18923174883559</v>
+        <v>-13.2097052631103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.510081548157906</v>
       </c>
       <c r="E23">
-        <v>-34.46939110083942</v>
+        <v>-38.82892358125714</v>
       </c>
       <c r="F23">
-        <v>-1.103406236961519</v>
+        <v>-3.050606415617371</v>
       </c>
       <c r="G23">
-        <v>-11.71222654830576</v>
+        <v>-13.67617483143828</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.227259760775148</v>
       </c>
       <c r="E24">
-        <v>-35.01104876861223</v>
+        <v>-39.30991321460252</v>
       </c>
       <c r="F24">
-        <v>-1.361744208668184</v>
+        <v>-2.851594460564401</v>
       </c>
       <c r="G24">
-        <v>-10.99187251147038</v>
+        <v>-12.90154210918135</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.860965482838566</v>
       </c>
       <c r="E25">
-        <v>-37.24590008892513</v>
+        <v>-39.71418057514434</v>
       </c>
       <c r="F25">
-        <v>-2.470661426713021</v>
+        <v>-3.111912230363757</v>
       </c>
       <c r="G25">
-        <v>-10.7376003473912</v>
+        <v>-13.29871337845512</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.442589176260389</v>
       </c>
       <c r="E26">
-        <v>-35.23058751924268</v>
+        <v>-39.78946583682951</v>
       </c>
       <c r="F26">
-        <v>-1.829063537120511</v>
+        <v>-3.348238823443234</v>
       </c>
       <c r="G26">
-        <v>-12.06926806246953</v>
+        <v>-13.1097307151105</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.007740226901374</v>
       </c>
       <c r="E27">
-        <v>-34.53764912896298</v>
+        <v>-39.83156694002929</v>
       </c>
       <c r="F27">
-        <v>-1.627736295176717</v>
+        <v>-3.102586470143041</v>
       </c>
       <c r="G27">
-        <v>-10.65624824055981</v>
+        <v>-13.09634673296416</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.596645711335301</v>
       </c>
       <c r="E28">
-        <v>-35.61360912725234</v>
+        <v>-39.14934798817898</v>
       </c>
       <c r="F28">
-        <v>-1.402606744280881</v>
+        <v>-3.175961597948215</v>
       </c>
       <c r="G28">
-        <v>-11.19676635772554</v>
+        <v>-13.2564741417155</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.252748411258894</v>
       </c>
       <c r="E29">
-        <v>-33.38557115011783</v>
+        <v>-39.47626801761286</v>
       </c>
       <c r="F29">
-        <v>-1.576996306653039</v>
+        <v>-3.129123219891722</v>
       </c>
       <c r="G29">
-        <v>-11.09619133846979</v>
+        <v>-13.32715352465841</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.007567693966919</v>
       </c>
       <c r="E30">
-        <v>-33.95595450401882</v>
+        <v>-39.43560392553147</v>
       </c>
       <c r="F30">
-        <v>-1.477824989557285</v>
+        <v>-3.147303399280963</v>
       </c>
       <c r="G30">
-        <v>-11.82678079947463</v>
+        <v>-13.26590937266778</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.890956210942041</v>
       </c>
       <c r="E31">
-        <v>-34.41387512506044</v>
+        <v>-38.92821440439981</v>
       </c>
       <c r="F31">
-        <v>-2.579518843849709</v>
+        <v>-3.111536151562886</v>
       </c>
       <c r="G31">
-        <v>-11.53661742412912</v>
+        <v>-13.44359926028354</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.91416085668029</v>
       </c>
       <c r="E32">
-        <v>-34.03859510296026</v>
+        <v>-38.94678341223312</v>
       </c>
       <c r="F32">
-        <v>-1.971338952020938</v>
+        <v>-3.084761660369601</v>
       </c>
       <c r="G32">
-        <v>-11.32244760234173</v>
+        <v>-13.18213057873896</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.077992549061795</v>
       </c>
       <c r="E33">
-        <v>-33.35121163282752</v>
+        <v>-38.97869253484178</v>
       </c>
       <c r="F33">
-        <v>-1.920251877555486</v>
+        <v>-2.932953393397758</v>
       </c>
       <c r="G33">
-        <v>-12.59878972341749</v>
+        <v>-13.50391529257204</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.371651403905277</v>
       </c>
       <c r="E34">
-        <v>-32.85911838900521</v>
+        <v>-38.16871872603408</v>
       </c>
       <c r="F34">
-        <v>-2.356255604712381</v>
+        <v>-3.102860659753367</v>
       </c>
       <c r="G34">
-        <v>-11.47427675941022</v>
+        <v>-13.23369278441345</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.768896989023469</v>
       </c>
       <c r="E35">
-        <v>-33.58753143381593</v>
+        <v>-38.24264588761603</v>
       </c>
       <c r="F35">
-        <v>-1.19319380811836</v>
+        <v>-3.222628503952328</v>
       </c>
       <c r="G35">
-        <v>-10.66317976744921</v>
+        <v>-13.72333140561526</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.243781408912156</v>
       </c>
       <c r="E36">
-        <v>-33.37475826443364</v>
+        <v>-37.47678333628933</v>
       </c>
       <c r="F36">
-        <v>-1.10210155830211</v>
+        <v>-3.145252361591632</v>
       </c>
       <c r="G36">
-        <v>-11.92177926828377</v>
+        <v>-13.7702673718743</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.759002926735358</v>
       </c>
       <c r="E37">
-        <v>-33.45129156612192</v>
+        <v>-37.58388634993401</v>
       </c>
       <c r="F37">
-        <v>-1.10013087225085</v>
+        <v>-3.042777515293513</v>
       </c>
       <c r="G37">
-        <v>-12.36452108439542</v>
+        <v>-13.48908365254992</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.285476401436272</v>
       </c>
       <c r="E38">
-        <v>-30.93076991125335</v>
+        <v>-37.56370589610667</v>
       </c>
       <c r="F38">
-        <v>-1.567171869255837</v>
+        <v>-3.227161330380447</v>
       </c>
       <c r="G38">
-        <v>-11.39594267332616</v>
+        <v>-14.01466569990989</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.793604746755046</v>
       </c>
       <c r="E39">
-        <v>-32.20334708687141</v>
+        <v>-36.23029455760818</v>
       </c>
       <c r="F39">
-        <v>-1.191814576392699</v>
+        <v>-2.924110571372873</v>
       </c>
       <c r="G39">
-        <v>-12.60101146706453</v>
+        <v>-13.89776308398132</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.2577559671138</v>
       </c>
       <c r="E40">
-        <v>-30.65544107289649</v>
+        <v>-36.45764134552929</v>
       </c>
       <c r="F40">
-        <v>-1.109042448770167</v>
+        <v>-3.024877324086419</v>
       </c>
       <c r="G40">
-        <v>-13.89550740065459</v>
+        <v>-14.22372629453247</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.66671861239451</v>
       </c>
       <c r="E41">
-        <v>-30.92201701838627</v>
+        <v>-36.10226143549203</v>
       </c>
       <c r="F41">
-        <v>-1.049770275997654</v>
+        <v>-2.758012138335336</v>
       </c>
       <c r="G41">
-        <v>-12.89646290557934</v>
+        <v>-13.82964223073769</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.00742810971683</v>
       </c>
       <c r="E42">
-        <v>-29.80960220769323</v>
+        <v>-35.3973576433855</v>
       </c>
       <c r="F42">
-        <v>-1.461563309072927</v>
+        <v>-2.974400756396831</v>
       </c>
       <c r="G42">
-        <v>-13.30115311927552</v>
+        <v>-14.32239416486441</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.28423888152728</v>
       </c>
       <c r="E43">
-        <v>-30.61395256836711</v>
+        <v>-35.10335389030655</v>
       </c>
       <c r="F43">
-        <v>-1.026279433189066</v>
+        <v>-2.81759826235351</v>
       </c>
       <c r="G43">
-        <v>-13.06925764708676</v>
+        <v>-13.85043420066132</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.49948504696514</v>
       </c>
       <c r="E44">
-        <v>-28.77385152484521</v>
+        <v>-34.97471439933697</v>
       </c>
       <c r="F44">
-        <v>-1.215239149809064</v>
+        <v>-2.81995082577746</v>
       </c>
       <c r="G44">
-        <v>-12.44831554279179</v>
+        <v>-14.01869016269709</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.66740564561996</v>
       </c>
       <c r="E45">
-        <v>-29.29420114191598</v>
+        <v>-34.24724621010266</v>
       </c>
       <c r="F45">
-        <v>-0.7496627063722268</v>
+        <v>-2.759412079246067</v>
       </c>
       <c r="G45">
-        <v>-12.76860821609105</v>
+        <v>-14.27798278862499</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.80374279536501</v>
       </c>
       <c r="E46">
-        <v>-28.37077613595361</v>
+        <v>-33.99133363468937</v>
       </c>
       <c r="F46">
-        <v>-0.9303536595774801</v>
+        <v>-2.631945388405487</v>
       </c>
       <c r="G46">
-        <v>-13.24538761480934</v>
+        <v>-14.20465480529439</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.92124437889887</v>
       </c>
       <c r="E47">
-        <v>-29.36864122509655</v>
+        <v>-33.94231743463374</v>
       </c>
       <c r="F47">
-        <v>-0.6928242770291386</v>
+        <v>-2.495070100603911</v>
       </c>
       <c r="G47">
-        <v>-12.86531019574588</v>
+        <v>-14.73089737103591</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.04046503306143</v>
       </c>
       <c r="E48">
-        <v>-28.15809018400914</v>
+        <v>-33.17337320050403</v>
       </c>
       <c r="F48">
-        <v>-0.8617217635207355</v>
+        <v>-2.531856240227432</v>
       </c>
       <c r="G48">
-        <v>-14.83969362500908</v>
+        <v>-14.49244631917887</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.16836521371134</v>
       </c>
       <c r="E49">
-        <v>-29.24662195297875</v>
+        <v>-33.29398453398271</v>
       </c>
       <c r="F49">
-        <v>-0.1042120799892968</v>
+        <v>-2.703310896891471</v>
       </c>
       <c r="G49">
-        <v>-13.50251854421579</v>
+        <v>-14.67417763942168</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.31983660498244</v>
       </c>
       <c r="E50">
-        <v>-27.67259223977065</v>
+        <v>-32.84688302844227</v>
       </c>
       <c r="F50">
-        <v>-0.3884721528317667</v>
+        <v>-2.629353426802128</v>
       </c>
       <c r="G50">
-        <v>-13.30529114945243</v>
+        <v>-14.52938704977083</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.49476502703864</v>
       </c>
       <c r="E51">
-        <v>-25.95278065584975</v>
+        <v>-32.66612073534609</v>
       </c>
       <c r="F51">
-        <v>-0.2436528216373431</v>
+        <v>-2.59157987323447</v>
       </c>
       <c r="G51">
-        <v>-12.97339763256256</v>
+        <v>-14.40711282684604</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.69536031580694</v>
       </c>
       <c r="E52">
-        <v>-26.25074449592693</v>
+        <v>-31.96701274964337</v>
       </c>
       <c r="F52">
-        <v>-1.065837290142353</v>
+        <v>-2.460721017879427</v>
       </c>
       <c r="G52">
-        <v>-13.83071133064775</v>
+        <v>-14.72999274803509</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.91457129913547</v>
       </c>
       <c r="E53">
-        <v>-24.99845991084198</v>
+        <v>-31.29797609053806</v>
       </c>
       <c r="F53">
-        <v>-0.9796125271849527</v>
+        <v>-2.367644828133471</v>
       </c>
       <c r="G53">
-        <v>-15.00434545413682</v>
+        <v>-14.87839660820004</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.14186224445312</v>
       </c>
       <c r="E54">
-        <v>-24.55115489794662</v>
+        <v>-31.58334116406137</v>
       </c>
       <c r="F54">
-        <v>-0.6489796187663637</v>
+        <v>-2.675651709311995</v>
       </c>
       <c r="G54">
-        <v>-15.58711064027595</v>
+        <v>-14.65564004745248</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.3715499151913</v>
       </c>
       <c r="E55">
-        <v>-25.1443622246832</v>
+        <v>-31.09169439045648</v>
       </c>
       <c r="F55">
-        <v>-1.007777847247539</v>
+        <v>-2.728830411469515</v>
       </c>
       <c r="G55">
-        <v>-14.75744211666605</v>
+        <v>-15.22853661903719</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.58715493139328</v>
       </c>
       <c r="E56">
-        <v>-25.86910590728844</v>
+        <v>-31.32112401385699</v>
       </c>
       <c r="F56">
-        <v>-1.07394700701576</v>
+        <v>-2.683523684740798</v>
       </c>
       <c r="G56">
-        <v>-13.98390851788199</v>
+        <v>-15.09093993610716</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.78361185851418</v>
       </c>
       <c r="E57">
-        <v>-24.87584465289907</v>
+        <v>-29.78816748404579</v>
       </c>
       <c r="F57">
-        <v>-1.332246045454494</v>
+        <v>-2.543587579385878</v>
       </c>
       <c r="G57">
-        <v>-14.1479807617105</v>
+        <v>-15.61630398629377</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.94705414935298</v>
       </c>
       <c r="E58">
-        <v>-23.5851843951727</v>
+        <v>-30.09083483594834</v>
       </c>
       <c r="F58">
-        <v>-1.000874233312608</v>
+        <v>-2.610503098184022</v>
       </c>
       <c r="G58">
-        <v>-15.29321520553744</v>
+        <v>-15.10088948374389</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.07421424151027</v>
       </c>
       <c r="E59">
-        <v>-23.07772426944852</v>
+        <v>-29.685186532641</v>
       </c>
       <c r="F59">
-        <v>-0.1777984414821852</v>
+        <v>-2.5712310279847</v>
       </c>
       <c r="G59">
-        <v>-16.25703031310021</v>
+        <v>-15.60381548954218</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.15869833546037</v>
       </c>
       <c r="E60">
-        <v>-23.85018004375338</v>
+        <v>-29.89158659924535</v>
       </c>
       <c r="F60">
-        <v>-0.7334391307883984</v>
+        <v>-2.622658561452702</v>
       </c>
       <c r="G60">
-        <v>-15.32425826409807</v>
+        <v>-15.49538473981177</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.19895945926561</v>
       </c>
       <c r="E61">
-        <v>-23.94612753177957</v>
+        <v>-29.94992468211955</v>
       </c>
       <c r="F61">
-        <v>-1.291646102308484</v>
+        <v>-2.939782454266437</v>
       </c>
       <c r="G61">
-        <v>-15.09308727353335</v>
+        <v>-15.12934398904244</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.20036726889816</v>
       </c>
       <c r="E62">
-        <v>-23.8254435171027</v>
+        <v>-28.90836365662809</v>
       </c>
       <c r="F62">
-        <v>-0.9996275403713943</v>
+        <v>-2.803454717318111</v>
       </c>
       <c r="G62">
-        <v>-14.62645192292383</v>
+        <v>-15.51818698307055</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.16135912707414</v>
       </c>
       <c r="E63">
-        <v>-22.94024882138537</v>
+        <v>-29.33506458814097</v>
       </c>
       <c r="F63">
-        <v>-0.8541098954564108</v>
+        <v>-2.908599391755452</v>
       </c>
       <c r="G63">
-        <v>-14.85486335645574</v>
+        <v>-15.82547031607229</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.09256577308997</v>
       </c>
       <c r="E64">
-        <v>-21.86347894688767</v>
+        <v>-28.85676415912842</v>
       </c>
       <c r="F64">
-        <v>-0.6596639015276716</v>
+        <v>-2.932029763743636</v>
       </c>
       <c r="G64">
-        <v>-15.79955345451631</v>
+        <v>-15.61134226619836</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.99523235011811</v>
       </c>
       <c r="E65">
-        <v>-21.84047015614813</v>
+        <v>-28.9493807716721</v>
       </c>
       <c r="F65">
-        <v>-0.6504980162156951</v>
+        <v>-3.025882133746014</v>
       </c>
       <c r="G65">
-        <v>-15.90729105155778</v>
+        <v>-15.95353517050017</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.87964003846349</v>
       </c>
       <c r="E66">
-        <v>-24.13029753476777</v>
+        <v>-28.89656853646558</v>
       </c>
       <c r="F66">
-        <v>-1.552205755389458</v>
+        <v>-2.94195526196398</v>
       </c>
       <c r="G66">
-        <v>-15.04106818755542</v>
+        <v>-15.9445072157041</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.74898323218214</v>
       </c>
       <c r="E67">
-        <v>-23.01248147274679</v>
+        <v>-28.88372265383788</v>
       </c>
       <c r="F67">
-        <v>-0.7165710853651921</v>
+        <v>-3.059614082755413</v>
       </c>
       <c r="G67">
-        <v>-16.78165813331212</v>
+        <v>-16.07182278643433</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.60937499778132</v>
       </c>
       <c r="E68">
-        <v>-20.941175307983</v>
+        <v>-29.03023964295518</v>
       </c>
       <c r="F68">
-        <v>-1.446202892322816</v>
+        <v>-3.111706795247863</v>
       </c>
       <c r="G68">
-        <v>-15.8355451794494</v>
+        <v>-15.66437432107765</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.46977364578437</v>
       </c>
       <c r="E69">
-        <v>-21.00834934795078</v>
+        <v>-28.54134852506431</v>
       </c>
       <c r="F69">
-        <v>-0.6373244894089746</v>
+        <v>-3.177084864146411</v>
       </c>
       <c r="G69">
-        <v>-15.4426437829544</v>
+        <v>-15.71398107905339</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.3299471154995</v>
       </c>
       <c r="E70">
-        <v>-21.99719158549053</v>
+        <v>-29.02172971295061</v>
       </c>
       <c r="F70">
-        <v>-1.391747675997582</v>
+        <v>-2.97880352914271</v>
       </c>
       <c r="G70">
-        <v>-15.24441125152346</v>
+        <v>-15.95023257859241</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.19871191166203</v>
       </c>
       <c r="E71">
-        <v>-21.67431263067571</v>
+        <v>-28.71957528264668</v>
       </c>
       <c r="F71">
-        <v>-0.8724135015886687</v>
+        <v>-3.125340065963137</v>
       </c>
       <c r="G71">
-        <v>-15.37145661018851</v>
+        <v>-15.56840073916373</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.07282820071033</v>
       </c>
       <c r="E72">
-        <v>-21.43615088046474</v>
+        <v>-28.70670448075104</v>
       </c>
       <c r="F72">
-        <v>-0.953032702331325</v>
+        <v>-3.223931525876932</v>
       </c>
       <c r="G72">
-        <v>-16.2380815288579</v>
+        <v>-15.62721298256774</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.95729787552712</v>
       </c>
       <c r="E73">
-        <v>-22.67730485919915</v>
+        <v>-29.09813634169348</v>
       </c>
       <c r="F73">
-        <v>-1.118983685971164</v>
+        <v>-3.31492851344186</v>
       </c>
       <c r="G73">
-        <v>-15.64334999488541</v>
+        <v>-15.45531633719966</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.85122933052621</v>
       </c>
       <c r="E74">
-        <v>-22.1748161274308</v>
+        <v>-29.06202001601277</v>
       </c>
       <c r="F74">
-        <v>-0.6582846698020105</v>
+        <v>-3.569024415678789</v>
       </c>
       <c r="G74">
-        <v>-14.98028744272971</v>
+        <v>-15.77809313397736</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.75503249876824</v>
       </c>
       <c r="E75">
-        <v>-24.72135765124942</v>
+        <v>-29.14220399045557</v>
       </c>
       <c r="F75">
-        <v>-0.6247821785631873</v>
+        <v>-3.186001410870145</v>
       </c>
       <c r="G75">
-        <v>-14.598905956743</v>
+        <v>-15.47581198761219</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.67350617262006</v>
       </c>
       <c r="E76">
-        <v>-22.54241686179137</v>
+        <v>-29.33401174907013</v>
       </c>
       <c r="F76">
-        <v>-1.504582913402514</v>
+        <v>-3.368396315822957</v>
       </c>
       <c r="G76">
-        <v>-16.40222034667349</v>
+        <v>-14.98703882824233</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.60300126461963</v>
       </c>
       <c r="E77">
-        <v>-22.79161369449241</v>
+        <v>-29.32316563769534</v>
       </c>
       <c r="F77">
-        <v>-1.32723525103496</v>
+        <v>-3.498305862134392</v>
       </c>
       <c r="G77">
-        <v>-15.76261402929665</v>
+        <v>-15.55253785502813</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.55100036241293</v>
       </c>
       <c r="E78">
-        <v>-24.78483948634942</v>
+        <v>-29.91227166824866</v>
       </c>
       <c r="F78">
-        <v>-0.6247863204002013</v>
+        <v>-3.558778339273562</v>
       </c>
       <c r="G78">
-        <v>-15.96743738544785</v>
+        <v>-15.30174711886119</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.51518738443932</v>
       </c>
       <c r="E79">
-        <v>-24.11699479889434</v>
+        <v>-29.86754781209724</v>
       </c>
       <c r="F79">
-        <v>-1.665005372996069</v>
+        <v>-3.567976530914247</v>
       </c>
       <c r="G79">
-        <v>-14.7772876916754</v>
+        <v>-14.78978532603306</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.49947915278643</v>
       </c>
       <c r="E80">
-        <v>-25.14276739153447</v>
+        <v>-30.60656400542024</v>
       </c>
       <c r="F80">
-        <v>-1.600790331931051</v>
+        <v>-3.702735340001671</v>
       </c>
       <c r="G80">
-        <v>-14.84515660806598</v>
+        <v>-14.56678074454935</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.50428153313302</v>
       </c>
       <c r="E81">
-        <v>-26.85113272504414</v>
+        <v>-30.73762897180352</v>
       </c>
       <c r="F81">
-        <v>-0.8921659223084228</v>
+        <v>-3.646427894163777</v>
       </c>
       <c r="G81">
-        <v>-14.18003026231101</v>
+        <v>-14.57166022619014</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.52588915891451</v>
       </c>
       <c r="E82">
-        <v>-26.27128627913953</v>
+        <v>-31.47621946096573</v>
       </c>
       <c r="F82">
-        <v>-1.05167469265669</v>
+        <v>-3.718438700856541</v>
       </c>
       <c r="G82">
-        <v>-15.23448128447116</v>
+        <v>-14.58350125828313</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.56614606928494</v>
       </c>
       <c r="E83">
-        <v>-24.16244339042194</v>
+        <v>-31.51373126565158</v>
       </c>
       <c r="F83">
-        <v>-1.746622756459099</v>
+        <v>-3.793545116533567</v>
       </c>
       <c r="G83">
-        <v>-15.71329053710904</v>
+        <v>-14.38687041865884</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.61676375747238</v>
       </c>
       <c r="E84">
-        <v>-26.36734590387149</v>
+        <v>-32.51090484510894</v>
       </c>
       <c r="F84">
-        <v>-0.7078732276357973</v>
+        <v>-3.760122976932815</v>
       </c>
       <c r="G84">
-        <v>-14.7135072013145</v>
+        <v>-14.40290561193746</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.68031127054132</v>
       </c>
       <c r="E85">
-        <v>-27.7533099018687</v>
+        <v>-32.94376498901654</v>
       </c>
       <c r="F85">
-        <v>-0.9333689169236703</v>
+        <v>-3.710979252394332</v>
       </c>
       <c r="G85">
-        <v>-15.23266812235263</v>
+        <v>-13.94776667513491</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.7511806341755</v>
       </c>
       <c r="E86">
-        <v>-28.80353867939508</v>
+        <v>-33.98556067094786</v>
       </c>
       <c r="F86">
-        <v>-1.18958378297696</v>
+        <v>-3.761459961920933</v>
       </c>
       <c r="G86">
-        <v>-14.27191541819524</v>
+        <v>-13.91995310763348</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.8285585015793</v>
       </c>
       <c r="E87">
-        <v>-27.81171235951844</v>
+        <v>-34.17704863229041</v>
       </c>
       <c r="F87">
-        <v>-1.9033896307041</v>
+        <v>-3.774430538713968</v>
       </c>
       <c r="G87">
-        <v>-14.01634571405427</v>
+        <v>-13.94561803233642</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.91534214146534</v>
       </c>
       <c r="E88">
-        <v>-32.30312798895041</v>
+        <v>-34.86511322908041</v>
       </c>
       <c r="F88">
-        <v>-1.084042320553678</v>
+        <v>-3.770243969860219</v>
       </c>
       <c r="G88">
-        <v>-13.75775668379368</v>
+        <v>-13.85929637317585</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.00910957129914</v>
       </c>
       <c r="E89">
-        <v>-31.56787045187638</v>
+        <v>-35.99409935295952</v>
       </c>
       <c r="F89">
-        <v>-0.4006822883490314</v>
+        <v>-4.018207468214223</v>
       </c>
       <c r="G89">
-        <v>-13.97593791464532</v>
+        <v>-13.71529683913611</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.11666532098418</v>
       </c>
       <c r="E90">
-        <v>-32.30244686229315</v>
+        <v>-36.8352180934921</v>
       </c>
       <c r="F90">
-        <v>-1.019869526226203</v>
+        <v>-3.921483148426339</v>
       </c>
       <c r="G90">
-        <v>-12.86951871602676</v>
+        <v>-13.94921563838298</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.2339103138312</v>
       </c>
       <c r="E91">
-        <v>-33.96654311629147</v>
+        <v>-37.80220197982928</v>
       </c>
       <c r="F91">
-        <v>-1.179829756808996</v>
+        <v>-4.181972390278075</v>
       </c>
       <c r="G91">
-        <v>-13.65505129695158</v>
+        <v>-13.92229364015942</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.36512884700284</v>
       </c>
       <c r="E92">
-        <v>-35.06730816921836</v>
+        <v>-38.55326248599429</v>
       </c>
       <c r="F92">
-        <v>-1.76308987205935</v>
+        <v>-4.159353818344634</v>
       </c>
       <c r="G92">
-        <v>-14.10916290575753</v>
+        <v>-13.71011320575046</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.50282659803326</v>
       </c>
       <c r="E93">
-        <v>-36.09159183559854</v>
+        <v>-39.74404216456985</v>
       </c>
       <c r="F93">
-        <v>-1.435671029163623</v>
+        <v>-4.155737994631414</v>
       </c>
       <c r="G93">
-        <v>-13.75406248019726</v>
+        <v>-13.58860262561857</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.63775189094566</v>
       </c>
       <c r="E94">
-        <v>-38.50452870430875</v>
+        <v>-41.17469886963354</v>
       </c>
       <c r="F94">
-        <v>-1.155882483561465</v>
+        <v>-4.231109487877336</v>
       </c>
       <c r="G94">
-        <v>-13.45332820000233</v>
+        <v>-13.74575900702522</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.76137333184327</v>
       </c>
       <c r="E95">
-        <v>-38.0242222742263</v>
+        <v>-42.845081008972</v>
       </c>
       <c r="F95">
-        <v>-1.572386442056459</v>
+        <v>-4.482976253433331</v>
       </c>
       <c r="G95">
-        <v>-13.87172482280185</v>
+        <v>-14.30209040417933</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.85098721186543</v>
       </c>
       <c r="E96">
-        <v>-43.1100974236093</v>
+        <v>-44.19503251157162</v>
       </c>
       <c r="F96">
-        <v>-1.849174640925678</v>
+        <v>-4.512780912586058</v>
       </c>
       <c r="G96">
-        <v>-13.52243069321221</v>
+        <v>-14.15030954588577</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.89866720589817</v>
       </c>
       <c r="E97">
-        <v>-43.71079506697022</v>
+        <v>-45.444989221709</v>
       </c>
       <c r="F97">
-        <v>-1.896144729399215</v>
+        <v>-4.499168351055853</v>
       </c>
       <c r="G97">
-        <v>-13.96534090234999</v>
+        <v>-14.3539515401095</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.87287887837802</v>
       </c>
       <c r="E98">
-        <v>-46.10834532602478</v>
+        <v>-46.89006795309816</v>
       </c>
       <c r="F98">
-        <v>-2.46247964187557</v>
+        <v>-4.751630712774461</v>
       </c>
       <c r="G98">
-        <v>-13.90639028948265</v>
+        <v>-14.43346437737644</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.77603365090288</v>
       </c>
       <c r="E99">
-        <v>-46.47891664478543</v>
+        <v>-48.20631199258547</v>
       </c>
       <c r="F99">
-        <v>-1.952219403996922</v>
+        <v>-4.838149546159856</v>
       </c>
       <c r="G99">
-        <v>-13.93816696727339</v>
+        <v>-14.4276907157132</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.57264317850344</v>
       </c>
       <c r="E100">
-        <v>-48.81375860434922</v>
+        <v>-49.9594593272051</v>
       </c>
       <c r="F100">
-        <v>-1.762037845457795</v>
+        <v>-4.800123340534344</v>
       </c>
       <c r="G100">
-        <v>-14.03564303269949</v>
+        <v>-14.67926859137435</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.2932988433843</v>
       </c>
       <c r="E101">
-        <v>-49.76038864028625</v>
+        <v>-51.14803365056719</v>
       </c>
       <c r="F101">
-        <v>-2.50479016370836</v>
+        <v>-4.858731162649812</v>
       </c>
       <c r="G101">
-        <v>-15.05633451655195</v>
+        <v>-14.52318914211153</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.88870669474917</v>
       </c>
       <c r="E102">
-        <v>-52.34902192257918</v>
+        <v>-52.78507380938991</v>
       </c>
       <c r="F102">
-        <v>-2.841504945598304</v>
+        <v>-5.078666021562692</v>
       </c>
       <c r="G102">
-        <v>-15.85390393541411</v>
+        <v>-15.16872315508249</v>
       </c>
     </row>
   </sheetData>
